--- a/data/trans_bre/P74B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P74B-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,8; 91,63</t>
+          <t>69,48; 91,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,12; 56,24</t>
+          <t>24,65; 56,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,46; 44,9</t>
+          <t>15,25; 44,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462,08; 2125,71</t>
+          <t>521,69; 2093,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,09; 281,04</t>
+          <t>65,46; 280,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,17; 388,76</t>
+          <t>65,33; 369,77</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,03; 80,51</t>
+          <t>63,97; 81,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,44; 68,68</t>
+          <t>51,27; 68,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49,52; 65,71</t>
+          <t>49,28; 65,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>770,69; 2844,85</t>
+          <t>807,03; 3085,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>399,66; 1338,09</t>
+          <t>411,53; 1292,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>553,82; 1674,25</t>
+          <t>564,4; 1889,13</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,22; 89,7</t>
+          <t>70,89; 90,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,19; 72,36</t>
+          <t>48,4; 72,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,61; 62,54</t>
+          <t>38,54; 62,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1070,14; 6953,45</t>
+          <t>937,64; 6280,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>341,79; 1264,14</t>
+          <t>352,36; 1253,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>209,03; 723,74</t>
+          <t>222,35; 767,34</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,82; 79,4</t>
+          <t>59,05; 79,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,77; 68,26</t>
+          <t>46,87; 68,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,65; 63,04</t>
+          <t>42,83; 63,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313,98; 860,49</t>
+          <t>324,12; 835,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>163,06; 461,2</t>
+          <t>166,52; 490,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>187,57; 520,11</t>
+          <t>198,66; 549,94</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,62; 84,03</t>
+          <t>55,89; 84,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,38; 64,38</t>
+          <t>35,01; 64,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,52; 50,44</t>
+          <t>22,45; 50,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280,46; 1408,67</t>
+          <t>282,07; 1452,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>141,24; 656,35</t>
+          <t>136,08; 648,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,37; 299,65</t>
+          <t>70,61; 291,16</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,34; 88,52</t>
+          <t>68,9; 89,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,24; 60,24</t>
+          <t>37,26; 60,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,83; 77,86</t>
+          <t>53,26; 77,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>973,69; 6446,09</t>
+          <t>1071,09; 11266,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>261,43; 1112,69</t>
+          <t>255,93; 1048,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>560,48; 6260,95</t>
+          <t>542,45; 6272,29</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,72; 79,55</t>
+          <t>63,81; 80,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,53; 62,21</t>
+          <t>45,43; 62,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,66; 66,73</t>
+          <t>49,06; 67,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>543,48; 1381,13</t>
+          <t>541,31; 1346,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>261,34; 678,71</t>
+          <t>271,95; 678,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>343,54; 985,48</t>
+          <t>373,78; 1071,14</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>65,65; 81,62</t>
+          <t>67,35; 81,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,99; 65,8</t>
+          <t>51,13; 65,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,97; 64,2</t>
+          <t>47,9; 64,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>568,2; 1367,88</t>
+          <t>580,68; 1343,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>418,01; 1005,17</t>
+          <t>420,01; 988,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>260,99; 547,63</t>
+          <t>259,07; 554,88</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>71,91; 78,22</t>
+          <t>71,58; 78,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51,29; 58,99</t>
+          <t>51,8; 59,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49,88; 57,51</t>
+          <t>49,85; 57,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>810,39; 1228,21</t>
+          <t>803,46; 1228,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>366,32; 545,53</t>
+          <t>363,35; 533,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>363,85; 527,04</t>
+          <t>358,18; 518,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P74B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P74B-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,48; 91,2</t>
+          <t>68,97; 92,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,65; 56,48</t>
+          <t>23,18; 54,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,25; 44,93</t>
+          <t>16,46; 45,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>521,69; 2093,13</t>
+          <t>479,71; 2281,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,46; 280,28</t>
+          <t>60,4; 273,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,33; 369,77</t>
+          <t>63,63; 373,74</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,97; 81,41</t>
+          <t>64,74; 81,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,27; 68,57</t>
+          <t>50,8; 67,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49,28; 65,14</t>
+          <t>49,07; 67,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>807,03; 3085,56</t>
+          <t>801,15; 2928,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>411,53; 1292,39</t>
+          <t>417,45; 1286,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>564,4; 1889,13</t>
+          <t>558,69; 1723,12</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,89; 90,02</t>
+          <t>69,33; 89,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,4; 72,47</t>
+          <t>47,12; 71,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,54; 62,55</t>
+          <t>38,62; 63,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>937,64; 6280,18</t>
+          <t>927,88; 6227,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>352,36; 1253,04</t>
+          <t>341,46; 1260,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>222,35; 767,34</t>
+          <t>218,1; 718,11</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,05; 79,02</t>
+          <t>59,2; 79,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,87; 68,4</t>
+          <t>47,33; 68,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,83; 63,28</t>
+          <t>43,44; 63,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324,12; 835,87</t>
+          <t>308,92; 854,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>166,52; 490,05</t>
+          <t>180,92; 493,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>198,66; 549,94</t>
+          <t>197,75; 536,6</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,89; 84,62</t>
+          <t>56,78; 84,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,01; 64,12</t>
+          <t>34,95; 63,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,45; 50,92</t>
+          <t>23,51; 51,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282,07; 1452,41</t>
+          <t>290,88; 1362,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>136,08; 648,01</t>
+          <t>141,82; 726,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,61; 291,16</t>
+          <t>77,36; 305,23</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,9; 89,18</t>
+          <t>69,3; 88,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,26; 60,33</t>
+          <t>35,27; 59,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,26; 77,73</t>
+          <t>52,8; 78,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1071,09; 11266,01</t>
+          <t>1185,27; 11193,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>255,93; 1048,38</t>
+          <t>254,64; 1084,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>542,45; 6272,29</t>
+          <t>559,44; 5999,01</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>63,81; 80,02</t>
+          <t>64,05; 80,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45,43; 62,12</t>
+          <t>44,68; 61,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,06; 67,56</t>
+          <t>48,34; 67,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>541,31; 1346,62</t>
+          <t>539,09; 1343,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>271,95; 678,34</t>
+          <t>263,67; 628,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>373,78; 1071,14</t>
+          <t>353,74; 1096,85</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>67,35; 81,55</t>
+          <t>66,86; 81,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,13; 65,96</t>
+          <t>50,73; 65,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,9; 64,19</t>
+          <t>48,08; 64,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>580,68; 1343,75</t>
+          <t>565,2; 1306,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>420,01; 988,79</t>
+          <t>424,93; 1035,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>259,07; 554,88</t>
+          <t>263,06; 552,25</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>71,58; 78,49</t>
+          <t>71,72; 78,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51,8; 59,19</t>
+          <t>51,66; 59,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49,85; 57,32</t>
+          <t>50,14; 57,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>803,46; 1228,43</t>
+          <t>802,34; 1210,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>363,35; 533,68</t>
+          <t>357,72; 529,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>358,18; 518,0</t>
+          <t>352,6; 512,46</t>
         </is>
       </c>
     </row>
